--- a/artfynd/A 3218-2022 artfynd.xlsx
+++ b/artfynd/A 3218-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3218-2022 artfynd.xlsx
+++ b/artfynd/A 3218-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,118 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123232206</v>
+      </c>
+      <c r="B3" t="n">
+        <v>90385</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4189</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kamjordstjärna</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Geastrum pectinatum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Solberga, Solberga, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>661022</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6573614</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ekerö</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ekerö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Lukas Bommelin</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lukas Bommelin</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3218-2022 artfynd.xlsx
+++ b/artfynd/A 3218-2022 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>123232206</v>
       </c>
       <c r="B3" t="n">
-        <v>90385</v>
+        <v>90388</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 3218-2022 artfynd.xlsx
+++ b/artfynd/A 3218-2022 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>123232206</v>
       </c>
       <c r="B3" t="n">
-        <v>90388</v>
+        <v>90390</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 3218-2022 artfynd.xlsx
+++ b/artfynd/A 3218-2022 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>123232206</v>
       </c>
       <c r="B3" t="n">
-        <v>90390</v>
+        <v>90396</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 3218-2022 artfynd.xlsx
+++ b/artfynd/A 3218-2022 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>123232206</v>
       </c>
       <c r="B3" t="n">
-        <v>90399</v>
+        <v>90416</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 3218-2022 artfynd.xlsx
+++ b/artfynd/A 3218-2022 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>123232206</v>
       </c>
       <c r="B3" t="n">
-        <v>90416</v>
+        <v>90421</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 3218-2022 artfynd.xlsx
+++ b/artfynd/A 3218-2022 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>123232206</v>
       </c>
       <c r="B3" t="n">
-        <v>90421</v>
+        <v>90423</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 3218-2022 artfynd.xlsx
+++ b/artfynd/A 3218-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>87593169</v>
+        <v>115609443</v>
       </c>
       <c r="B2" t="n">
-        <v>90126</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>232138</v>
+        <v>1445</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ekerö, Upl</t>
+          <t>Rödstensvägen, Jungfrusundsåsen, Jungfrusundsåsen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>660908.790416115</v>
+        <v>661032</v>
       </c>
       <c r="R2" t="n">
-        <v>6573546.495260051</v>
+        <v>6573599</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,22 +747,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-08-22</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-08-22</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>10 fruktkroppar av varierande storlek. Fyndplats invid vägen mot Rödsten, nära en vägbom. Det pågår avverkning för granbarkborre nära lokalen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,71 +776,74 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Martina Kiibus</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Brian Johnson, Charlotta Brandt</t>
+          <t>Martina Kiibus</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123232206</v>
+        <v>122806826</v>
       </c>
       <c r="B3" t="n">
-        <v>90423</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4189</v>
+        <v>1445</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Solberga, Solberga, Upl</t>
+          <t>Solberga, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>661022</v>
+        <v>661040</v>
       </c>
       <c r="R3" t="n">
-        <v>6573614</v>
+        <v>6573615</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +867,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,15 +897,687 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>David Morger</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>David Morger</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>115832102</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91333</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2008</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fyrflikig jordstjärna</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Geastrum quadrifidum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Pers., nom.sanct.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Solberga, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>661036</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6573591</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ekerö</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ekerö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Malin Löfgren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Malin Löfgren, Johan Frössling</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131745116</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91398</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2008</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fyrflikig jordstjärna</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Geastrum quadrifidum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Pers., nom.sanct.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skog, ekebyhov, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>661023</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6573630</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ekerö</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ekerö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Emelie Envall</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Emelie Envall</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123232206</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4189</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kamjordstjärna</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Geastrum pectinatum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Pers., nom.sanct</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Solberga, Solberga, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>661022</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6573614</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ekerö</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ekerö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Lukas Bommelin</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Lukas Bommelin</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131745136</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106358</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221157</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåbär</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Vaccinium myrtillus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skog, ekebyhov, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>661023</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6573630</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ekerö</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ekerö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Emelie Envall</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Emelie Envall</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>87575415</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92688</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>232138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gul lammticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Albatrellus citrinus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Ryman</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ekerö, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>660879</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6573550</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ekerö</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ekerö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2020-08-21</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2020-08-21</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Brian Johnson, Charlotta Brandt, Majken Ekstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>87593169</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92688</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>232138</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gul lammticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Albatrellus citrinus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Ryman</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ekerö, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>660909</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6573546</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ekerö</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ekerö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2020-08-22</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2020-08-22</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Brian Johnson, Charlotta Brandt</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
